--- a/pc-gaming-occasion.xlsx
+++ b/pc-gaming-occasion.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +102,15 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -160,6 +167,24 @@
         <fgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,6 +271,25 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -611,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2023,6 +2067,434 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600 + RX 6600 + MSI B550 + Corsair 4000D</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>600 €</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Nouveau (23/05)</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600 (6C/12T Zen 3)</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>AMD RX 6600 8 Go</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="inlineStr">
+        <is>
+          <t>+40-50% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>MSI B550 Gaming Plus ✅✅</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="inlineStr">
+        <is>
+          <t>B550 PCIe 4.0 ✅✅</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 3200 MHz ✅ (dual channel non confirmé)</t>
+        </is>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>1 To SSD</t>
+        </is>
+      </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>650W (marque inconnue ⚠️)</t>
+        </is>
+      </c>
+      <c r="N14" s="25" t="inlineStr">
+        <is>
+          <t>Corsair 4000D ✅</t>
+        </is>
+      </c>
+      <c r="O14" s="25" t="inlineStr">
+        <is>
+          <t>Belin-Béliet (33) – Gironde</t>
+        </is>
+      </c>
+      <c r="P14" s="25" t="inlineStr">
+        <is>
+          <t>Très bon état</t>
+        </is>
+      </c>
+      <c r="Q14" s="25" t="inlineStr">
+        <is>
+          <t>1/1 (2 avis)</t>
+        </is>
+      </c>
+      <c r="R14" s="25" t="inlineStr">
+        <is>
+          <t>Mondial Relay ✅</t>
+        </is>
+      </c>
+      <c r="S14" s="25" t="inlineStr">
+        <is>
+          <t>MSI B550 Gaming Plus ✅✅ + Corsair 4000D (excellent boîtier ATX) + DDR4 3200 + Livraison Mondial Relay. Config propre et complète, composants premium.</t>
+        </is>
+      </c>
+      <c r="T14" s="25" t="inlineStr">
+        <is>
+          <t>Prix élevé (600€) vs deals existants (300-450€). Marque alim inconnue (demander avant achat). Dual channel RAM non confirmé.</t>
+        </is>
+      </c>
+      <c r="U14" s="25" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3197584091</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ Annonce ancienne (fév. 2026) — vérifier disponibilité</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Ryzen 7 5800 + RX 6700 XT + Asus — Prix Négociable</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>400 € (négociable)</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>Nouveau (23/05)</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>Ryzen 7 5800 (8C/16T Zen 3)</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>AMD RX 6700 XT</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
+        <is>
+          <t>+70-80% vs 1660 Ti (≈ RTX 3060 Ti)</t>
+        </is>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Asus (type inconnu ⚠️ CRITIQUE)</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>Inconnu ⚠️ (demander !)</t>
+        </is>
+      </c>
+      <c r="K15" s="27" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 (fréq. inconnue ⚠️)</t>
+        </is>
+      </c>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>2 To Crucial</t>
+        </is>
+      </c>
+      <c r="M15" s="27" t="inlineStr">
+        <is>
+          <t>Non précisée ⚠️ CRITIQUE</t>
+        </is>
+      </c>
+      <c r="N15" s="27" t="inlineStr">
+        <is>
+          <t>Asus (risque format propriétaire ⚠️)</t>
+        </is>
+      </c>
+      <c r="O15" s="27" t="inlineStr">
+        <is>
+          <t>Caen (14) – Basse-Normandie</t>
+        </is>
+      </c>
+      <c r="P15" s="27" t="inlineStr">
+        <is>
+          <t>État quasi neuf (2025)</t>
+        </is>
+      </c>
+      <c r="Q15" s="27" t="inlineStr">
+        <is>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="R15" s="27" t="inlineStr">
+        <is>
+          <t>Mondial Relay ✅</t>
+        </is>
+      </c>
+      <c r="S15" s="27" t="inlineStr">
+        <is>
+          <t>RX 6700 XT = excellent GPU (≈ RTX 3060 Ti) pour 400€ négociable. Ryzen 7 5800 Zen 3. 2 To stockage. État quasi neuf.</t>
+        </is>
+      </c>
+      <c r="T15" s="27" t="inlineStr">
+        <is>
+          <t>⚠️ Marque Asus = probable PC pré-monté format propriétaire (boîtier non-ATX, alim non upgradable). CM, alim, chipset non précisés. Annonce de 3 mois (toujours dispo = suspect ou invendable). Demander IMPÉRATIVEMENT : modèle CM + alim.</t>
+        </is>
+      </c>
+      <c r="U15" s="27" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3138550431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600 + RX 6600 (CM/Alim/Boîtier inconnus)</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>600 €</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>Nouveau (23/05)</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600 (6C/12T Zen 3)</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>AMD RX 6600 8 Go</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>+40-50% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
+        <is>
+          <t>Non précisée ⚠️ CRITIQUE</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="inlineStr">
+        <is>
+          <t>Inconnu ⚠️</t>
+        </is>
+      </c>
+      <c r="K16" s="27" t="inlineStr">
+        <is>
+          <t>16 Go DDR4 (fréq. inconnue ⚠️)</t>
+        </is>
+      </c>
+      <c r="L16" s="27" t="inlineStr">
+        <is>
+          <t>1 To SSD</t>
+        </is>
+      </c>
+      <c r="M16" s="27" t="inlineStr">
+        <is>
+          <t>Non précisée ⚠️ CRITIQUE</t>
+        </is>
+      </c>
+      <c r="N16" s="27" t="inlineStr">
+        <is>
+          <t>Non précisé ⚠️</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="inlineStr">
+        <is>
+          <t>Creuzier-le-Vieux (03) – Allier, Auvergne</t>
+        </is>
+      </c>
+      <c r="P16" s="27" t="inlineStr">
+        <is>
+          <t>Excellent état</t>
+        </is>
+      </c>
+      <c r="Q16" s="27" t="inlineStr">
+        <is>
+          <t>Non précisé (0 avis)</t>
+        </is>
+      </c>
+      <c r="R16" s="27" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S16" s="27" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600 Zen 3. RX 6600 (+40-50%). SSD 1 To.</t>
+        </is>
+      </c>
+      <c r="T16" s="27" t="inlineStr">
+        <is>
+          <t>CM/alim/boîtier entièrement inconnus. Pas de livraison. 1 seule photo. Aucun avis vendeur. Overpriced à 600€ vu les infos manquantes.</t>
+        </is>
+      </c>
+      <c r="U16" s="27" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3193745756</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>✅ Disponible</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Ryzen 7 5800X + RTX 2070 + MSI A520M PRO — CHIPSET DISQUALIFIÉ</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>670 €</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Nouveau (23/05)</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Ryzen 7 5800X (8C/16T Zen 3)</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>MSI RTX 2070 8 Go</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>+25-30% vs 1660 Ti</t>
+        </is>
+      </c>
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>MSI A520M PRO ❌❌</t>
+        </is>
+      </c>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>A520 ❌ (liste noire : bas de gamme, pas d'OC, limité)</t>
+        </is>
+      </c>
+      <c r="K17" s="29" t="inlineStr">
+        <is>
+          <t>16 Go Corsair LPX 3200 MHz ✅</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>500 Go SSD</t>
+        </is>
+      </c>
+      <c r="M17" s="29" t="inlineStr">
+        <is>
+          <t>Non précisée ⚠️</t>
+        </is>
+      </c>
+      <c r="N17" s="29" t="inlineStr">
+        <is>
+          <t>BeQuiet (ATX présumé)</t>
+        </is>
+      </c>
+      <c r="O17" s="29" t="inlineStr">
+        <is>
+          <t>Grenoble (38) – Isère, Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="P17" s="29" t="inlineStr">
+        <is>
+          <t>Excellent état</t>
+        </is>
+      </c>
+      <c r="Q17" s="29" t="inlineStr">
+        <is>
+          <t>1/1 (12 avis)</t>
+        </is>
+      </c>
+      <c r="R17" s="29" t="inlineStr">
+        <is>
+          <t>❌ Face à face uniquement</t>
+        </is>
+      </c>
+      <c r="S17" s="29" t="inlineStr">
+        <is>
+          <t>5800X Zen 3. RTX 2070. DDR4 3200. Vendeur avec 12 avis positifs. Cooling BeQuiet silencieux.</t>
+        </is>
+      </c>
+      <c r="T17" s="29" t="inlineStr">
+        <is>
+          <t>❌ MSI A520M PRO = chipset A520 DISQUALIFIÉ (liste noire). Prix très élevé (670€) pour ces specs. Alim inconnue. SSD 500 Go insuffisant. Pas de livraison.</t>
+        </is>
+      </c>
+      <c r="U17" s="29" t="inlineStr">
+        <is>
+          <t>https://www.leboncoin.fr/ad/ordinateurs/3189825357</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2035,7 +2507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2128,7 +2600,6 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -2162,6 +2633,43 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>--- Recherche du 23/05 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>🔍 Ryzen 5 5600 + RX 6600 + B550 + Corsair 4000D @ 600€</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐ — Config la plus complète et propre de la nouvelle recherche | ID: 3197584091
+MSI B550 Gaming Plus ✅✅ + Corsair 4000D ✅ + DDR4 3200 + RX 6600. Livraison Mondial Relay.
+⚠️ Prix élevé (600€) vs deals existants. Demander marque alim avant achat.
+→ https://www.leboncoin.fr/ad/ordinateurs/3197584091</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>⚠️ À INVESTIGUER — Ryzen 7 5800 + RX 6700 XT @ 400€</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐ — Annonce Asus (format propriétaire possible !) | ID: 3138550431
+RX 6700 XT ≈ RTX 3060 Ti. 400€ négociable. État quasi neuf. 2 To stockage.
+⚠️ DEMANDER IMPÉRATIVEMENT : modèle exact CM + marque alim + dimensions boîtier.
+→ https://www.leboncoin.fr/ad/ordinateurs/3138550431</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
